--- a/backend/data/financials_by_company/1660.HK.xlsx
+++ b/backend/data/financials_by_company/1660.HK.xlsx
@@ -4115,7 +4115,7 @@
         <v>-70042000</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE2" t="n">
         <v>3.5087686</v>
